--- a/assets/tableau.xlsx
+++ b/assets/tableau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shaki\Desktop\Informatique\4. Développement\PortfolioOral.github.io-main\PortfolioOral.github.io-main\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8996356-8DFD-49DE-9FDD-349C639D2D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036336B9-5117-405D-9CA3-68272E0186E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="76">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -117,9 +117,6 @@
 → Outils : GLPI</t>
   </si>
   <si>
-    <t>03/09/24 au 21/04/25</t>
-  </si>
-  <si>
     <t>✓</t>
   </si>
   <si>
@@ -194,9 +191,6 @@
 → Migration des rôles AD/DNS/DHCP, tests de continuité de service</t>
   </si>
   <si>
-    <t>03/09/25 au 21/04/26</t>
-  </si>
-  <si>
     <t>Installation et configuration d'une infrastructure Multi-WAN
 → Fortinet, load balancing, failover</t>
   </si>
@@ -223,12 +217,84 @@
   <si>
     <t xml:space="preserve">Adresse URL du portfolio :  https://shakimgr.github.io/PortfolioOral.github.io/ </t>
   </si>
+  <si>
+    <t>09/2024 au 05/2026</t>
+  </si>
+  <si>
+    <t>09/2024 au 05/2027</t>
+  </si>
+  <si>
+    <t>09/2024 au 05/2028</t>
+  </si>
+  <si>
+    <t>09/2024 au 05/2029</t>
+  </si>
+  <si>
+    <t>09/2024 au 05/2030</t>
+  </si>
+  <si>
+    <t>09/2024 au 05/2031</t>
+  </si>
+  <si>
+    <t>09/2024 au 05/2032</t>
+  </si>
+  <si>
+    <t>09/2024 au 05/2033</t>
+  </si>
+  <si>
+    <t>09/2024 au 05/2034</t>
+  </si>
+  <si>
+    <t>09/2024 au 05/2035</t>
+  </si>
+  <si>
+    <t>05/2025 au 06/2025</t>
+  </si>
+  <si>
+    <t>05/2025 au 06/2026</t>
+  </si>
+  <si>
+    <t>05/2025 au 06/2027</t>
+  </si>
+  <si>
+    <t>05/2025 au 06/2028</t>
+  </si>
+  <si>
+    <t>05/2025 au 06/2029</t>
+  </si>
+  <si>
+    <t>05/2025 au 06/2030</t>
+  </si>
+  <si>
+    <t>05/2025 au 06/2031</t>
+  </si>
+  <si>
+    <t>01/2026 au 02/2026</t>
+  </si>
+  <si>
+    <t>01/2026 au 02/2027</t>
+  </si>
+  <si>
+    <t>01/2026 au 02/2028</t>
+  </si>
+  <si>
+    <t>01/2026 au 02/2029</t>
+  </si>
+  <si>
+    <t>01/2026 au 02/2030</t>
+  </si>
+  <si>
+    <t>01/2026 au 02/2031</t>
+  </si>
+  <si>
+    <t>01/2026 au 02/2032</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -300,6 +366,11 @@
       <sz val="12"/>
       <color rgb="FF1F497D"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -717,11 +788,20 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -746,15 +826,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -983,56 +1054,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="34" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="35"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="22" t="s">
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="23"/>
-      <c r="H3" s="24"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="29"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="33"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="38"/>
       <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1044,22 +1115,22 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
+      <c r="A5" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="30" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1082,8 +1153,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="324.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="29"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="31"/>
       <c r="C7" s="7" t="s">
         <v>17</v>
       </c>
@@ -1104,26 +1175,26 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>26</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
@@ -1133,13 +1204,13 @@
     </row>
     <row r="10" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>26</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="15"/>
@@ -1149,34 +1220,34 @@
     </row>
     <row r="11" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>26</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
       <c r="F11" s="15"/>
       <c r="G11" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H11" s="16"/>
     </row>
     <row r="12" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>26</v>
-      </c>
       <c r="D12" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
@@ -1185,76 +1256,76 @@
     </row>
     <row r="13" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>26</v>
-      </c>
       <c r="D13" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H13" s="16"/>
     </row>
     <row r="14" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
       <c r="E14" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G14" s="15"/>
       <c r="H14" s="16"/>
     </row>
     <row r="15" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>26</v>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
       <c r="F15" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H15" s="16"/>
     </row>
     <row r="16" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>26</v>
-      </c>
       <c r="D16" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
@@ -1263,28 +1334,28 @@
     </row>
     <row r="17" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>26</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
       <c r="F17" s="15"/>
       <c r="G17" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H17" s="16"/>
     </row>
     <row r="18" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
@@ -1292,141 +1363,141 @@
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="21"/>
+      <c r="A19" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B20" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>26</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
       <c r="G20" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H20" s="16"/>
     </row>
     <row r="21" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>26</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="15"/>
       <c r="G21" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H21" s="16"/>
     </row>
     <row r="22" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B22" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>26</v>
       </c>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="15"/>
       <c r="G22" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H22" s="16"/>
     </row>
     <row r="23" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>26</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
       <c r="G23" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H23" s="16"/>
     </row>
     <row r="24" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="14" t="s">
-        <v>26</v>
-      </c>
       <c r="D24" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
       <c r="G24" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H24" s="16"/>
     </row>
     <row r="25" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B25" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>26</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
       <c r="F25" s="15"/>
       <c r="G25" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H25" s="16"/>
     </row>
     <row r="26" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="C26" s="15"/>
       <c r="D26" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="15"/>
@@ -1434,121 +1505,121 @@
       <c r="H26" s="16"/>
     </row>
     <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="21"/>
+      <c r="A27" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
       <c r="F28" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H28" s="16"/>
     </row>
     <row r="29" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
       <c r="F29" s="15"/>
       <c r="G29" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H29" s="16"/>
     </row>
     <row r="30" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D30" s="15"/>
       <c r="E30" s="15"/>
       <c r="F30" s="15"/>
       <c r="G30" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H30" s="16"/>
     </row>
     <row r="31" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="15"/>
       <c r="F31" s="15"/>
       <c r="G31" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H31" s="16"/>
     </row>
     <row r="32" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D32" s="15"/>
       <c r="E32" s="15"/>
       <c r="F32" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H32" s="16"/>
     </row>
     <row r="33" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="15"/>
@@ -1557,22 +1628,22 @@
     </row>
     <row r="34" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D34" s="15"/>
       <c r="E34" s="15"/>
       <c r="F34" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G34" s="15"/>
       <c r="H34" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11237,11 +11308,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="B6:B7"/>
@@ -11249,7 +11315,13 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
+  <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A5" r:id="rId1" display="Adresse URL du portfolio : https://shakimguerin.wixsite.com/portfolio-shakim-gue " xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
